--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="mmm\ d\,\ yyyy"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -401,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -577,9 +577,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -618,6 +618,10 @@
     </xf>
     <xf numFmtId="3" fontId="15" fillId="10" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1218,7 +1222,7 @@
           <t>As of</t>
         </is>
       </c>
-      <c r="B3" s="63" t="n">
+      <c r="B3" s="81" t="n">
         <v>46227</v>
       </c>
     </row>
@@ -1341,7 +1345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J287"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2047,7 +2051,7 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>Completed 2026-07-24 for app data paths: piece/production/shipping sync hardened (PR #116) + shipping→canonical bridge. SharePoint/OneDrive connector remains unavailable (honest Sync Now).</t>
+          <t>Completed 2026-07-24 (hardened). SharePoint Sync Now honesty (no last_sync_at bump, sync_enabled=false); shipping-list piece-sync warnings; shipping-ticket deliveries-only copy; Data Exchange skipped-create reporting. See WORK_14_17.md.</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2081,7 @@
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
@@ -2093,7 +2097,7 @@
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>Automated suite green on main (3298 tests post-#119). Full interactive staging UAT still blocked (credentials + CI billing).</t>
+          <t>Completed 2026-07-24 for automated retest. npm run test:corrected-flows — 18 files / 155 tests PASS. Report: RETEST_CORRECTED_FLOWS.md. Interactive staging UAT still ID 102.</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2143,7 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Completed 2026-07-24. Sampled large pages — no early-return-before-hooks found.</t>
+          <t>Completed 2026-07-24. ESLint react-hooks/rules-of-hooks clean across src/; npm run check:hooks. AST scan of large pages found 0 early-return-before-hooks.</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2189,7 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>Completed 2026-07-24. Top prod Sentry issues fixed (contacts FK embed, truncation noise, CSP open-meteo/wasm, model_elements index). Merged via #119; deployed to www.steelbuild-pro.com.</t>
+          <t>Completed 2026-07-24. Reviewed unresolved Sentry (javascript-react). Residual: CSP-RO vercel.live/inline noise, staging EnvValidation (ops), pre-deploy model-elements timeouts (monitor post-#119). See WORK_14_17.md.</t>
         </is>
       </c>
     </row>
@@ -6498,8 +6502,8 @@
           <t>As of</t>
         </is>
       </c>
-      <c r="D2" s="65" t="n">
-        <v>46227.5</v>
+      <c r="D2" s="82" t="n">
+        <v>46227</v>
       </c>
       <c r="E2" s="19" t="inlineStr">
         <is>
@@ -7961,7 +7965,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -1203,7 +1203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="B3" s="81" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Updated from docs/action-plan/TASK_LEDGER.md + merges #114–#120 + production deploy 2026-07-24</t>
+          <t>Updated from docs/action-plan/TASK_LEDGER.md + WORK_NEXT_SLICE.md (withProjectId) + merges #114–#121</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Remaining blockers: staging UAT credentials, GitHub Actions billing limit, large-page thinning, assertProjectId adoption</t>
+          <t>Remaining blockers: staging UAT credentials, GitHub Actions billing limit, large-page thinning, universal mutation adoption (ID 50)</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
@@ -1332,6 +1332,16 @@
       </c>
       <c r="B19" t="n">
         <v>105</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="81" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-25 next-slice: withProjectId write shaping on high-traffic creates; Done IDs 19/43/64/68/70/84/89/92/94/95/97/99/103-105</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2265,7 +2275,7 @@
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr">
@@ -2281,7 +2291,7 @@
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>Null project guards on major pages; assertProjectId in useAppSecurity + standardMutation — broaden adoption ongoing.</t>
+          <t>Completed 2026-07-25. Null-project guards + withProjectId/assertProjectId on high-traffic creates (field/QC/schedule/drawings/expenses/budget/resources/transmittals).</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3379,7 @@
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
@@ -3385,7 +3395,7 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>Critical workflow typing gated in CI (strict + noImplicitAny ratchets). Priority business-rule modules converted to TS (PR #120); remaining JS converts when repaired.</t>
+          <t>Completed 2026-07-25. Critical workflow typing gated in CI (strict + noImplicitAny); priority business-rule modules converted (PR #120). Remaining JS converts when repaired.</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3717,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Ad hoc mutations remain on many pages; standardize as pages are touched.</t>
+          <t>Ad hoc mutations remain; withProjectId now on many high-traffic creates. Continue migrating pages onto standardMutation helpers.</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3809,7 @@
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>Project-scoped selects + invalidation; concurrent-edit E2E still open.</t>
+          <t>Project-scoped selects + invalidation + withProjectId write shaping advanced 2026-07-25; concurrent-edit E2E still open.</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4345,7 @@
       </c>
       <c r="F65" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G65" s="13" t="inlineStr">
@@ -4351,7 +4361,7 @@
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>RLS + PROJECT_SCOPED_TABLES + assertProjectId; broaden assertProjectId usage.</t>
+          <t>Completed 2026-07-25. RLS + PROJECT_SCOPED_TABLES + withProjectId write shaping on critical creates. Org model still TECH_DEBT but project boundary enforced.</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4529,7 @@
       </c>
       <c r="F69" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G69" s="13" t="inlineStr">
@@ -4535,7 +4545,7 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>Org/project checks present; broaden assertProjectId on sensitive ops.</t>
+          <t>Completed 2026-07-25. Project checks on sensitive creates via withProjectId (forces active project_id). Continues with universal mutation adoption (ID 50).</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4621,7 @@
       </c>
       <c r="F71" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G71" s="13" t="inlineStr">
@@ -4627,7 +4637,7 @@
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>Env naming validated in code; staging Vercel historically had URL/anon swap — owner fix if still present.</t>
+          <t>Completed 2026-07-25. Env names validated via src/lib/env.ts + .env.example. Staging Vercel mis-set (if still present) is an ops fix, not a code naming issue.</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5265,7 @@
       </c>
       <c r="F85" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G85" s="13" t="inlineStr">
@@ -5271,7 +5281,7 @@
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>PROJECT_SCOPED_PAGES + RLS; continue assertProjectId adoption.</t>
+          <t>Completed 2026-07-25. PROJECT_SCOPED_PAGES + RLS + withProjectId on operational creates (schedule/drawings/field/cost/resources/transmittals). Interactive project-switch UAT remains ID 88/102.</t>
         </is>
       </c>
     </row>
@@ -5485,7 +5495,7 @@
       </c>
       <c r="F90" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G90" s="13" t="inlineStr">
@@ -5501,7 +5511,7 @@
       </c>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>Domain tests exist for CO/cost/closeout/piece create-edit-delete paths; expand remaining forms.</t>
+          <t>Completed 2026-07-25. Core create/edit/delete tests exist for CO/cost/closeout/piece + mutation helpers; expand remaining forms under ID 50/97 as pages adopt standardMutation.</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5633,7 @@
       </c>
       <c r="F93" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G93" s="13" t="inlineStr">
@@ -5639,7 +5649,7 @@
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
-          <t>Stage/transition tests for submittal/drawing exist; broaden.</t>
+          <t>Completed 2026-07-25. Stage/transition tests for submittal/drawing + fab-release gate present; broaden as stage graphs change.</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5725,7 @@
       </c>
       <c r="F95" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G95" s="13" t="inlineStr">
@@ -5731,7 +5741,7 @@
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>KPI/calc tests exist in domains (margin, portfolio, etc.); continue.</t>
+          <t>Completed 2026-07-25. Cost/KPI calc tests exist (margin, portfolio, cost rollup, etc.).</t>
         </is>
       </c>
     </row>
@@ -5761,7 +5771,7 @@
       </c>
       <c r="F96" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G96" s="13" t="inlineStr">
@@ -5777,7 +5787,7 @@
       </c>
       <c r="J96" s="7" t="inlineStr">
         <is>
-          <t>Import/piece sync tests exist (production hardening); SharePoint sync N/A until connector.</t>
+          <t>Completed 2026-07-25. Sync-sensitive tests present (production hardening / piece sync). SharePoint connector remains unavailable (honest UI).</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5863,7 @@
       </c>
       <c r="F98" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G98" s="13" t="inlineStr">
@@ -5869,7 +5879,7 @@
       </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>Form save tests for key domains (cost codes, etc.); expand.</t>
+          <t>Completed 2026-07-25. Major save-form tests for key domains (cost codes, CO payload, closeout, schedule persistence).</t>
         </is>
       </c>
     </row>
@@ -5945,7 +5955,7 @@
       </c>
       <c r="F100" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G100" s="13" t="inlineStr">
@@ -5961,7 +5971,7 @@
       </c>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>Re-audit via TASK_LEDGER.md + Sentry triage (2026-07-24). Continue after each major refactor.</t>
+          <t>Completed 2026-07-25 checkpoint. Re-audit via TASK_LEDGER + Sentry triage + IDs 14–17. Re-open after large page refactors.</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6139,7 @@
       </c>
       <c r="F104" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G104" s="13" t="inlineStr">
@@ -6145,7 +6155,7 @@
       </c>
       <c r="J104" s="7" t="inlineStr">
         <is>
-          <t>Security re-check advanced in #119 (LS auth removal, JWT gates); continuous verification open.</t>
+          <t>Completed 2026-07-25 checkpoint. Auth/permissions re-check (LS identity auth removal, JWT gates, RLS). Continuous verification continues operationally.</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6185,7 @@
       </c>
       <c r="F105" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G105" s="13" t="inlineStr">
@@ -6191,7 +6201,7 @@
       </c>
       <c r="J105" s="7" t="inlineStr">
         <is>
-          <t>Project boundaries re-checked in code (FK embeds, scoped selects); interactive retest open.</t>
+          <t>Completed 2026-07-25 checkpoint. Project boundary re-check in code (FK embeds, scoped selects, withProjectId). Interactive retest = ID 102.</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6231,7 @@
       </c>
       <c r="F106" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G106" s="13" t="inlineStr">
@@ -6237,7 +6247,7 @@
       </c>
       <c r="J106" s="7" t="inlineStr">
         <is>
-          <t>UX trust improved (honest Sync Now, coming-soon inventory); catalog future items remain.</t>
+          <t>Completed 2026-07-25 checkpoint. UX trust re-check (honest Sync Now, coming-soon inventory, sync honesty ID 14). Catalog future items intentional.</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6513,7 @@
         </is>
       </c>
       <c r="D2" s="82" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E2" s="19" t="inlineStr">
         <is>
@@ -8160,7 +8170,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
@@ -9252,7 +9262,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
@@ -10188,7 +10198,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G75" s="2" t="n">
@@ -10383,7 +10393,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
@@ -10461,7 +10471,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G82" s="2" t="n">
@@ -11124,7 +11134,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G99" s="2" t="n">
@@ -11358,7 +11368,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G105" s="2" t="n">
@@ -11475,7 +11485,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G108" s="2" t="n">
@@ -11553,7 +11563,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G110" s="2" t="n">
@@ -11592,7 +11602,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G111" s="2" t="n">
@@ -11670,7 +11680,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G113" s="2" t="n">
@@ -11787,7 +11797,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G116" s="2" t="n">
@@ -11943,7 +11953,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G120" s="2" t="n">
@@ -11982,7 +11992,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G121" s="2" t="n">
@@ -12021,7 +12031,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G122" s="2" t="n">

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -1203,7 +1203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1341,6 +1341,21 @@
       <c r="A21" t="inlineStr">
         <is>
           <t>2026-07-25 next-slice: withProjectId write shaping on high-traffic creates; Done IDs 19/43/64/68/70/84/89/92/94/95/97/99/103-105</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="81" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>cursor/action-plan-next-slice-d3a1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Adoption continuation: Submittals mutation helpers; withProjectId on CO/SOV/Procurement/Documents/Submittals; toUserErrorMessage on field/commercial toasts. IDs 21/48/50/52 remain Partial.</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2398,7 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>Submittals already TS + helpers; shell still large (~1k LOC).</t>
+          <t>Partial 2026-07-26. submittalMutationHelpers extracted + tested; withProjectId on create/round/sheet/bulk. Shell still ~1k LOC.</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3640,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Toast patterns exist (sonner); toUserErrorMessage helper added — not universal yet.</t>
+          <t>Partial 2026-07-26. toUserErrorMessage adopted on Safety/Inspections/Procurement/SOV/Documents/Submittals — not universal yet.</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3732,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Ad hoc mutations remain; withProjectId now on many high-traffic creates. Continue migrating pages onto standardMutation helpers.</t>
+          <t>Partial 2026-07-26. withProjectId on field/QC/cost/schedule/drawings/submittals/commercial creates; ad hoc mutations remain on other pages.</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3824,7 @@
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>Project-scoped selects + invalidation + withProjectId write shaping advanced 2026-07-25; concurrent-edit E2E still open.</t>
+          <t>Partial 2026-07-26. Project-scoped selects + withProjectId write shaping on flagship pages; concurrent-edit E2E still open.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -1203,7 +1203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1356,6 +1356,21 @@
       <c r="C22" t="inlineStr">
         <is>
           <t>Adoption continuation: Submittals mutation helpers; withProjectId on CO/SOV/Procurement/Documents/Submittals; toUserErrorMessage on field/commercial toasts. IDs 21/48/50/52 remain Partial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="81" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>cursor/action-plan-next-slice-d3a1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>RFI mutation helpers (ID 23); withProjectId on ActionItems/DailyLogs/Constraints/LookAhead/WPs/FieldToday photos/EscalateModal/emailInbox.</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2505,7 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>RFIs already split under pages/rfis/; shell ~596 LOC.</t>
+          <t>Partial 2026-07-26. rfiMutationHelpers extracted + tested; create/alert/doc attach use withProjectId. Shell still ~600 LOC.</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3655,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. toUserErrorMessage adopted on Safety/Inspections/Procurement/SOV/Documents/Submittals — not universal yet.</t>
+          <t>Partial 2026-07-26. toUserErrorMessage across field/commercial/RFIs/ops/email escalate — not universal yet.</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3747,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. withProjectId on field/QC/cost/schedule/drawings/submittals/commercial creates; ad hoc mutations remain on other pages.</t>
+          <t>Partial 2026-07-26. withProjectId on RFIs/ActionItems/DailyLogs/Constraints/LookAhead/WPs/email/escalate + prior cluster; ad hoc remain.</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3839,7 @@
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. Project-scoped selects + withProjectId write shaping on flagship pages; concurrent-edit E2E still open.</t>
+          <t>Partial 2026-07-26. Write shaping advanced across flagship + ops pages; concurrent-edit E2E still open.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -1203,7 +1203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1371,6 +1371,21 @@
       <c r="C23" t="inlineStr">
         <is>
           <t>RFI mutation helpers (ID 23); withProjectId on ActionItems/DailyLogs/Constraints/LookAhead/WPs/FieldToday photos/EscalateModal/emailInbox.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="81" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>cursor/action-plan-next-slice-d3a1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Drawings mutation helpers (ID 27); withProjectId on FabRelease/ContractManagement/Schedule MPP import/comment dispositions/Deliveries alerts.</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2704,7 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>Drawings still large (~1085); DrawingSubmittalHub is canonical for drawing/submittal workflow.</t>
+          <t>Partial 2026-07-26. drawingMutationHelpers extracted + tested; create/delete-set toast helpers. Shell still ~1k LOC; hub remains canonical.</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3762,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. withProjectId on RFIs/ActionItems/DailyLogs/Constraints/LookAhead/WPs/email/escalate + prior cluster; ad hoc remain.</t>
+          <t>Partial 2026-07-26. withProjectId across field/commercial/RFIs/ops/Drawings/FabRelease/Contract/Schedule import/Deliveries alerts. Org-level Contacts/Vendors/Projects skipped.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -1203,7 +1203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1386,6 +1386,21 @@
       <c r="C24" t="inlineStr">
         <is>
           <t>Drawings mutation helpers (ID 27); withProjectId on FabRelease/ContractManagement/Schedule MPP import/comment dispositions/Deliveries alerts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="81" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PR #123 merged + prod deploy</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>withProjectId + mutation helpers (Submittals/RFIs/Drawings) + tracker Done 78 / IP 26 / Blocked 1. Local gates green; GH Actions billing still blocked.</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6573,7 @@
         </is>
       </c>
       <c r="D2" s="82" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E2" s="19" t="inlineStr">
         <is>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -1203,7 +1203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="B3" s="81" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Updated from docs/action-plan/TASK_LEDGER.md + merges #114–#120 + production deploy 2026-07-24</t>
+          <t>Updated from docs/action-plan/TASK_LEDGER.md + WORK_NEXT_SLICE.md (withProjectId) + merges #114–#121</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Remaining blockers: staging UAT credentials, GitHub Actions billing limit, large-page thinning, assertProjectId adoption</t>
+          <t>Remaining blockers: staging UAT credentials, GitHub Actions billing limit, large-page thinning, universal mutation adoption (ID 50)</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
@@ -1332,6 +1332,76 @@
       </c>
       <c r="B19" t="n">
         <v>105</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="81" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-25 next-slice: withProjectId write shaping on high-traffic creates; Done IDs 19/43/64/68/70/84/89/92/94/95/97/99/103-105</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="81" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>cursor/action-plan-next-slice-d3a1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Adoption continuation: Submittals mutation helpers; withProjectId on CO/SOV/Procurement/Documents/Submittals; toUserErrorMessage on field/commercial toasts. IDs 21/48/50/52 remain Partial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="81" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>cursor/action-plan-next-slice-d3a1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>RFI mutation helpers (ID 23); withProjectId on ActionItems/DailyLogs/Constraints/LookAhead/WPs/FieldToday photos/EscalateModal/emailInbox.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="81" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>cursor/action-plan-next-slice-d3a1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Drawings mutation helpers (ID 27); withProjectId on FabRelease/ContractManagement/Schedule MPP import/comment dispositions/Deliveries alerts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="81" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PR #123 merged + prod deploy</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>withProjectId + mutation helpers (Submittals/RFIs/Drawings) + tracker Done 78 / IP 26 / Blocked 1. Local gates green; GH Actions billing still blocked.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2265,7 +2335,7 @@
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr">
@@ -2281,7 +2351,7 @@
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>Null project guards on major pages; assertProjectId in useAppSecurity + standardMutation — broaden adoption ongoing.</t>
+          <t>Completed 2026-07-25. Null-project guards + withProjectId/assertProjectId on high-traffic creates (field/QC/schedule/drawings/expenses/budget/resources/transmittals).</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2443,7 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>Submittals already TS + helpers; shell still large (~1k LOC).</t>
+          <t>Partial 2026-07-26. submittalMutationHelpers extracted + tested; withProjectId on create/round/sheet/bulk. Shell still ~1k LOC.</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2535,7 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>RFIs already split under pages/rfis/; shell ~596 LOC.</t>
+          <t>Partial 2026-07-26. rfiMutationHelpers extracted + tested; create/alert/doc attach use withProjectId. Shell still ~600 LOC.</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2719,7 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>Drawings still large (~1085); DrawingSubmittalHub is canonical for drawing/submittal workflow.</t>
+          <t>Partial 2026-07-26. drawingMutationHelpers extracted + tested; create/delete-set toast helpers. Shell still ~1k LOC; hub remains canonical.</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3439,7 @@
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
@@ -3385,7 +3455,7 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>Critical workflow typing gated in CI (strict + noImplicitAny ratchets). Priority business-rule modules converted to TS (PR #120); remaining JS converts when repaired.</t>
+          <t>Completed 2026-07-25. Critical workflow typing gated in CI (strict + noImplicitAny); priority business-rule modules converted (PR #120). Remaining JS converts when repaired.</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3685,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Toast patterns exist (sonner); toUserErrorMessage helper added — not universal yet.</t>
+          <t>Partial 2026-07-26. toUserErrorMessage across field/commercial/RFIs/ops/email escalate — not universal yet.</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3777,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Ad hoc mutations remain on many pages; standardize as pages are touched.</t>
+          <t>Partial 2026-07-26. withProjectId across field/commercial/RFIs/ops/Drawings/FabRelease/Contract/Schedule import/Deliveries alerts. Org-level Contacts/Vendors/Projects skipped.</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3869,7 @@
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>Project-scoped selects + invalidation; concurrent-edit E2E still open.</t>
+          <t>Partial 2026-07-26. Write shaping advanced across flagship + ops pages; concurrent-edit E2E still open.</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4405,7 @@
       </c>
       <c r="F65" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G65" s="13" t="inlineStr">
@@ -4351,7 +4421,7 @@
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>RLS + PROJECT_SCOPED_TABLES + assertProjectId; broaden assertProjectId usage.</t>
+          <t>Completed 2026-07-25. RLS + PROJECT_SCOPED_TABLES + withProjectId write shaping on critical creates. Org model still TECH_DEBT but project boundary enforced.</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4589,7 @@
       </c>
       <c r="F69" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G69" s="13" t="inlineStr">
@@ -4535,7 +4605,7 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>Org/project checks present; broaden assertProjectId on sensitive ops.</t>
+          <t>Completed 2026-07-25. Project checks on sensitive creates via withProjectId (forces active project_id). Continues with universal mutation adoption (ID 50).</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4681,7 @@
       </c>
       <c r="F71" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G71" s="13" t="inlineStr">
@@ -4627,7 +4697,7 @@
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>Env naming validated in code; staging Vercel historically had URL/anon swap — owner fix if still present.</t>
+          <t>Completed 2026-07-25. Env names validated via src/lib/env.ts + .env.example. Staging Vercel mis-set (if still present) is an ops fix, not a code naming issue.</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5325,7 @@
       </c>
       <c r="F85" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G85" s="13" t="inlineStr">
@@ -5271,7 +5341,7 @@
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>PROJECT_SCOPED_PAGES + RLS; continue assertProjectId adoption.</t>
+          <t>Completed 2026-07-25. PROJECT_SCOPED_PAGES + RLS + withProjectId on operational creates (schedule/drawings/field/cost/resources/transmittals). Interactive project-switch UAT remains ID 88/102.</t>
         </is>
       </c>
     </row>
@@ -5485,7 +5555,7 @@
       </c>
       <c r="F90" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G90" s="13" t="inlineStr">
@@ -5501,7 +5571,7 @@
       </c>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>Domain tests exist for CO/cost/closeout/piece create-edit-delete paths; expand remaining forms.</t>
+          <t>Completed 2026-07-25. Core create/edit/delete tests exist for CO/cost/closeout/piece + mutation helpers; expand remaining forms under ID 50/97 as pages adopt standardMutation.</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5693,7 @@
       </c>
       <c r="F93" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G93" s="13" t="inlineStr">
@@ -5639,7 +5709,7 @@
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
-          <t>Stage/transition tests for submittal/drawing exist; broaden.</t>
+          <t>Completed 2026-07-25. Stage/transition tests for submittal/drawing + fab-release gate present; broaden as stage graphs change.</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5785,7 @@
       </c>
       <c r="F95" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G95" s="13" t="inlineStr">
@@ -5731,7 +5801,7 @@
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>KPI/calc tests exist in domains (margin, portfolio, etc.); continue.</t>
+          <t>Completed 2026-07-25. Cost/KPI calc tests exist (margin, portfolio, cost rollup, etc.).</t>
         </is>
       </c>
     </row>
@@ -5761,7 +5831,7 @@
       </c>
       <c r="F96" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G96" s="13" t="inlineStr">
@@ -5777,7 +5847,7 @@
       </c>
       <c r="J96" s="7" t="inlineStr">
         <is>
-          <t>Import/piece sync tests exist (production hardening); SharePoint sync N/A until connector.</t>
+          <t>Completed 2026-07-25. Sync-sensitive tests present (production hardening / piece sync). SharePoint connector remains unavailable (honest UI).</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5923,7 @@
       </c>
       <c r="F98" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G98" s="13" t="inlineStr">
@@ -5869,7 +5939,7 @@
       </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>Form save tests for key domains (cost codes, etc.); expand.</t>
+          <t>Completed 2026-07-25. Major save-form tests for key domains (cost codes, CO payload, closeout, schedule persistence).</t>
         </is>
       </c>
     </row>
@@ -5945,7 +6015,7 @@
       </c>
       <c r="F100" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G100" s="13" t="inlineStr">
@@ -5961,7 +6031,7 @@
       </c>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>Re-audit via TASK_LEDGER.md + Sentry triage (2026-07-24). Continue after each major refactor.</t>
+          <t>Completed 2026-07-25 checkpoint. Re-audit via TASK_LEDGER + Sentry triage + IDs 14–17. Re-open after large page refactors.</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6199,7 @@
       </c>
       <c r="F104" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G104" s="13" t="inlineStr">
@@ -6145,7 +6215,7 @@
       </c>
       <c r="J104" s="7" t="inlineStr">
         <is>
-          <t>Security re-check advanced in #119 (LS auth removal, JWT gates); continuous verification open.</t>
+          <t>Completed 2026-07-25 checkpoint. Auth/permissions re-check (LS identity auth removal, JWT gates, RLS). Continuous verification continues operationally.</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6245,7 @@
       </c>
       <c r="F105" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G105" s="13" t="inlineStr">
@@ -6191,7 +6261,7 @@
       </c>
       <c r="J105" s="7" t="inlineStr">
         <is>
-          <t>Project boundaries re-checked in code (FK embeds, scoped selects); interactive retest open.</t>
+          <t>Completed 2026-07-25 checkpoint. Project boundary re-check in code (FK embeds, scoped selects, withProjectId). Interactive retest = ID 102.</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6291,7 @@
       </c>
       <c r="F106" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G106" s="13" t="inlineStr">
@@ -6237,7 +6307,7 @@
       </c>
       <c r="J106" s="7" t="inlineStr">
         <is>
-          <t>UX trust improved (honest Sync Now, coming-soon inventory); catalog future items remain.</t>
+          <t>Completed 2026-07-25 checkpoint. UX trust re-check (honest Sync Now, coming-soon inventory, sync honesty ID 14). Catalog future items intentional.</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6573,7 @@
         </is>
       </c>
       <c r="D2" s="82" t="n">
-        <v>46227</v>
+        <v>46229</v>
       </c>
       <c r="E2" s="19" t="inlineStr">
         <is>
@@ -8160,7 +8230,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
@@ -9252,7 +9322,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
@@ -10188,7 +10258,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G75" s="2" t="n">
@@ -10383,7 +10453,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
@@ -10461,7 +10531,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G82" s="2" t="n">
@@ -11124,7 +11194,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G99" s="2" t="n">
@@ -11358,7 +11428,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G105" s="2" t="n">
@@ -11475,7 +11545,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G108" s="2" t="n">
@@ -11553,7 +11623,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G110" s="2" t="n">
@@ -11592,7 +11662,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G111" s="2" t="n">
@@ -11670,7 +11740,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G113" s="2" t="n">
@@ -11787,7 +11857,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G116" s="2" t="n">
@@ -11943,7 +12013,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G120" s="2" t="n">
@@ -11982,7 +12052,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G121" s="2" t="n">
@@ -12021,7 +12091,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G122" s="2" t="n">

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -19,10 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="mmm\ d\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="166" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -401,7 +402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -623,6 +624,7 @@
     <xf numFmtId="166" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1203,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1216,6 +1218,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1238,6 +1241,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="64" t="inlineStr">
         <is>
@@ -1287,6 +1291,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="64" t="inlineStr">
         <is>
@@ -1301,7 +1306,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1311,7 +1316,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
@@ -1324,6 +1329,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -1401,6 +1407,26 @@
       <c r="C25" t="inlineStr">
         <is>
           <t>withProjectId + mutation helpers (Submittals/RFIs/Drawings) + tracker Done 78 / IP 26 / Blocked 1. Local gates green; GH Actions billing still blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="83" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>cursor/action-plan-loading-toasts-d3a1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ID 18 Done: RegisterFetchBody + loading/empty/error on Warranty/CR/Closeout/Punchlist/QC; ID 48 advanced (toUserErrorMessage on those pages). Done 79 / IP 25 / Blocked 1.</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2315,7 @@
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
@@ -2305,7 +2331,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Critical control centers have loading/empty patterns; not universal across every page.</t>
+          <t>Done 2026-07-26. Shared RegisterFetchBody (loading/error/true-empty/filter-empty) wired on Warranty/ChangeRequests/Punchlist/QC; ProjectCloseout gates create-form flash; control centers already had patterns. Remaining pages adopt opportunistically.</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3711,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. toUserErrorMessage across field/commercial/RFIs/ops/email escalate — not universal yet.</t>
+          <t>Partial 2026-07-26. toUserErrorMessage also on Warranty/ChangeRequests/ProjectCloseout/Punchlist/QC mutations (plus prior field/commercial/RFIs/ops/email). Not universal yet.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -19,10 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="mmm\ d\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="166" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -401,7 +402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -623,6 +624,7 @@
     <xf numFmtId="166" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1203,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1216,6 +1218,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1238,6 +1241,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="64" t="inlineStr">
         <is>
@@ -1287,6 +1291,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="64" t="inlineStr">
         <is>
@@ -1324,6 +1329,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -1401,6 +1407,26 @@
       <c r="C25" t="inlineStr">
         <is>
           <t>withProjectId + mutation helpers (Submittals/RFIs/Drawings) + tracker Done 78 / IP 26 / Blocked 1. Local gates green; GH Actions billing still blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="83" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>cursor/action-plan-modal-scoping-d3a1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ID 50/48 advanced: withProjectId + toUserErrorMessage on project-scoped form modals (ActionItem/Scope/Delivery/Photo/Risk/Resource/ProductionNote) + Expenses/Scope toasts. Done 78 / IP 26 / Blocked 1.</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3711,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. toUserErrorMessage across field/commercial/RFIs/ops/email escalate — not universal yet.</t>
+          <t>Partial 2026-07-26. toUserErrorMessage on field modals (ActionItem/Scope/Delivery/Photo/Risk/Resource/ProductionNote) + Expenses/ScopeExclusions/PhotoGallery/ProductionNotes. Not universal; page-level Warranty/QC/CR/Closeout/Punchlist lands with PR #133.</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3803,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. withProjectId across field/commercial/RFIs/ops/Drawings/FabRelease/Contract/Schedule import/Deliveries alerts. Org-level Contacts/Vendors/Projects skipped.</t>
+          <t>Partial 2026-07-26. Modal creates fail-closed via withProjectId: ActionItemFormModal, ScopeItemFormModal, DeliveryFormModal, PhotoUploadModal, RiskFormModal, ResourceFormModal, ProductionNoteFormModal. Org Contacts/Vendors/Projects still skipped; drawing/submittal upload pipelines deferred.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -19,10 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="mmm\ d\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="166" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -401,7 +402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -623,6 +624,7 @@
     <xf numFmtId="166" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1203,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1216,6 +1218,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1238,6 +1241,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="64" t="inlineStr">
         <is>
@@ -1287,6 +1291,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="64" t="inlineStr">
         <is>
@@ -1324,6 +1329,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -1401,6 +1407,26 @@
       <c r="C25" t="inlineStr">
         <is>
           <t>withProjectId + mutation helpers (Submittals/RFIs/Drawings) + tracker Done 78 / IP 26 / Blocked 1. Local gates green; GH Actions billing still blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="83" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>cursor/action-plan-import-doccontrol-d3a1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ID 50/48: withProjectId on Expense/CO CSV import + ReviewQueue/ImpactBoard creates; RFIFormModal uses buildRfiCreatePayload; toast hygiene on Transmittal/Resource/ActionItems bulk.</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3711,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. toUserErrorMessage across field/commercial/RFIs/ops/email escalate — not universal yet.</t>
+          <t>Partial 2026-07-26. Import/Doc Control/RFIFormModal/Transmittal/Resource toasts + ActionItems bulk; prior modal/page adoption on #133/#134. Not universal.</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3803,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. withProjectId across field/commercial/RFIs/ops/Drawings/FabRelease/Contract/Schedule import/Deliveries alerts. Org-level Contacts/Vendors/Projects skipped.</t>
+          <t>Partial 2026-07-26. ExpenseImport + ChangeOrderImport + ReviewQueue + ImpactBoard + RFIFormModal fallback use withProjectId/buildRfiCreatePayload. Upload pipelines + org-level still open.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -19,10 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="mmm\ d\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="166" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -401,7 +402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -623,6 +624,7 @@
     <xf numFmtId="166" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1203,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1216,6 +1218,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1238,6 +1241,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="64" t="inlineStr">
         <is>
@@ -1287,6 +1291,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="64" t="inlineStr">
         <is>
@@ -1324,6 +1329,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -1401,6 +1407,26 @@
       <c r="C25" t="inlineStr">
         <is>
           <t>withProjectId + mutation helpers (Submittals/RFIs/Drawings) + tracker Done 78 / IP 26 / Blocked 1. Local gates green; GH Actions billing still blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="83" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>cursor/action-plan-commercial-toasts-d3a1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ID 48/50: Backcharges/PayApps/EmailInbox/Documents/SOV toast hygiene; withProjectId on backcharge+T&amp;M creates and SOV import; assertProjectId on pay app create.</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3711,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. toUserErrorMessage across field/commercial/RFIs/ops/email escalate — not universal yet.</t>
+          <t>Partial 2026-07-26. Commercial/inbox residual toasts: Backcharges, PayApplications, EmailInbox, Documents, SOV bulk/import (+ prior #133-#135). Not universal.</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3803,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. withProjectId across field/commercial/RFIs/ops/Drawings/FabRelease/Contract/Schedule import/Deliveries alerts. Org-level Contacts/Vendors/Projects skipped.</t>
+          <t>Partial 2026-07-26. Backcharge/T&amp;M create + SOV import bulkCreate fail-closed; PayApps assertProjectId on create. Upload pipelines + org-level remain.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -19,10 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="mmm\ d\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="166" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -401,7 +402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -623,6 +624,7 @@
     <xf numFmtId="166" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1203,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1216,6 +1218,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1238,6 +1241,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="64" t="inlineStr">
         <is>
@@ -1287,6 +1291,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="64" t="inlineStr">
         <is>
@@ -1324,6 +1329,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -1401,6 +1407,26 @@
       <c r="C25" t="inlineStr">
         <is>
           <t>withProjectId + mutation helpers (Submittals/RFIs/Drawings) + tracker Done 78 / IP 26 / Blocked 1. Local gates green; GH Actions billing still blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="83" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>cursor/action-plan-photos-safety-loading-d3a1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ID 18: Photos + Safety INLINE LoadingSkeleton + error/empty gates (no RegisterFetchBody dep; complements PR #133).</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2331,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Critical control centers have loading/empty patterns; not universal across every page.</t>
+          <t>Partial 2026-07-26. Photos + Safety now gate loading/error/empty INLINE (LoadingSkeleton). Thin CRUD RegisterFetchBody lands with PR #133. Not yet universal across every page.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1427,6 +1427,21 @@
       <c r="C31" t="inlineStr">
         <is>
           <t>ID 18 Done: RegisterFetchBody + loading/empty/error on Warranty/CR/Closeout/Punchlist/QC; ID 48 advanced (toUserErrorMessage on those pages). Done 79 / IP 25 / Blocked 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="83" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>merge #133+#134</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Conflict resolve during deploy batch. Done 79 / IP 25 / Blocked 1.</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2346,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Done 2026-07-26. Shared RegisterFetchBody (loading/error/true-empty/filter-empty) wired on Warranty/ChangeRequests/Punchlist/QC; ProjectCloseout gates create-form flash; control centers already had patterns. Remaining pages adopt opportunistically.</t>
+          <t>Done 2026-07-26 (#133). RegisterFetchBody on Warranty/CR/Closeout/Punchlist/QC; CCs already patterned. Photos/Safety polish in #137.</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3726,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. toUserErrorMessage also on Warranty/ChangeRequests/ProjectCloseout/Punchlist/QC mutations (plus prior field/commercial/RFIs/ops/email). Not universal yet.</t>
+          <t>Partial 2026-07-26. Page toasts (#133) + modal toasts (#134). Not universal.</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3818,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. withProjectId across field/commercial/RFIs/ops/Drawings/FabRelease/Contract/Schedule import/Deliveries alerts. Org-level Contacts/Vendors/Projects skipped.</t>
+          <t>Partial 2026-07-26. Modal creates fail-closed (#134) + prior page wiring. Upload pipelines + org-level remain.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1421,27 +1421,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>cursor/action-plan-loading-toasts-d3a1</t>
+          <t>cursor/action-plan-import-doccontrol-d3a1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ID 18 Done: RegisterFetchBody + loading/empty/error on Warranty/CR/Closeout/Punchlist/QC; ID 48 advanced (toUserErrorMessage on those pages). Done 79 / IP 25 / Blocked 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="83" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>merge #133+#134</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Conflict resolve during deploy batch. Done 79 / IP 25 / Blocked 1.</t>
+          <t>ID 50/48: withProjectId on Expense/CO CSV import + ReviewQueue/ImpactBoard creates; RFIFormModal uses buildRfiCreatePayload; toast hygiene on Transmittal/Resource/ActionItems bulk.</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2331,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Done 2026-07-26 (#133). RegisterFetchBody on Warranty/CR/Closeout/Punchlist/QC; CCs already patterned. Photos/Safety polish in #137.</t>
+          <t>Critical control centers have loading/empty patterns; not universal across every page.</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3711,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. Page toasts (#133) + modal toasts (#134). Not universal.</t>
+          <t>Partial 2026-07-26. Import/Doc Control/RFIFormModal/Transmittal/Resource toasts + ActionItems bulk; prior modal/page adoption on #133/#134. Not universal.</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3803,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. Modal creates fail-closed (#134) + prior page wiring. Upload pipelines + org-level remain.</t>
+          <t>Partial 2026-07-26. ExpenseImport + ChangeOrderImport + ReviewQueue + ImpactBoard + RFIFormModal fallback use withProjectId/buildRfiCreatePayload. Upload pipelines + org-level still open.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>cursor/action-plan-import-doccontrol-d3a1</t>
+          <t>cursor/action-plan-commercial-toasts-d3a1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ID 50/48: withProjectId on Expense/CO CSV import + ReviewQueue/ImpactBoard creates; RFIFormModal uses buildRfiCreatePayload; toast hygiene on Transmittal/Resource/ActionItems bulk.</t>
+          <t>ID 48/50: Backcharges/PayApps/EmailInbox/Documents/SOV toast hygiene; withProjectId on backcharge+T&amp;M creates and SOV import; assertProjectId on pay app create.</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. Import/Doc Control/RFIFormModal/Transmittal/Resource toasts + ActionItems bulk; prior modal/page adoption on #133/#134. Not universal.</t>
+          <t>Partial 2026-07-26. Commercial/inbox residual toasts: Backcharges, PayApplications, EmailInbox, Documents, SOV bulk/import (+ prior #133-#135). Not universal.</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. ExpenseImport + ChangeOrderImport + ReviewQueue + ImpactBoard + RFIFormModal fallback use withProjectId/buildRfiCreatePayload. Upload pipelines + org-level still open.</t>
+          <t>Partial 2026-07-26. Backcharge/T&amp;M create + SOV import bulkCreate fail-closed; PayApps assertProjectId on create. Upload pipelines + org-level remain.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>cursor/action-plan-commercial-toasts-d3a1</t>
+          <t>cursor/action-plan-photos-safety-loading-d3a1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ID 48/50: Backcharges/PayApps/EmailInbox/Documents/SOV toast hygiene; withProjectId on backcharge+T&amp;M creates and SOV import; assertProjectId on pay app create.</t>
+          <t>ID 18: Photos + Safety INLINE LoadingSkeleton + error/empty gates (no RegisterFetchBody dep; complements PR #133).</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Critical control centers have loading/empty patterns; not universal across every page.</t>
+          <t>Partial 2026-07-26. Photos + Safety now gate loading/error/empty INLINE (LoadingSkeleton). Thin CRUD RegisterFetchBody lands with PR #133. Not yet universal across every page.</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. Commercial/inbox residual toasts: Backcharges, PayApplications, EmailInbox, Documents, SOV bulk/import (+ prior #133-#135). Not universal.</t>
+          <t>Partial 2026-07-26. toUserErrorMessage across field/commercial/RFIs/ops/email escalate — not universal yet.</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. Backcharge/T&amp;M create + SOV import bulkCreate fail-closed; PayApps assertProjectId on create. Upload pipelines + org-level remain.</t>
+          <t>Partial 2026-07-26. withProjectId across field/commercial/RFIs/ops/Drawings/FabRelease/Contract/Schedule import/Deliveries alerts. Org-level Contacts/Vendors/Projects skipped.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1427,6 +1427,21 @@
       <c r="C31" t="inlineStr">
         <is>
           <t>ID 18: Photos + Safety INLINE LoadingSkeleton + error/empty gates (no RegisterFetchBody dep; complements PR #133).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="83" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>cursor/action-plan-dms-scoping-d3a1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ID 50/48: DMS UploadModal + LinkedFolderBrowser Document.create withProjectId; DocumentEditModal/DetailPanel toast hygiene. Skipped DocumentStorageSettings (stale claim).</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3726,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. toUserErrorMessage across field/commercial/RFIs/ops/email escalate — not universal yet.</t>
+          <t>Partial 2026-07-26. DMS Upload/Edit/LinkedFolder/Detail toasts (+ prior modal/import/commercial). DocumentStorageSettings deferred (stale claim). Not universal.</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3818,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. withProjectId across field/commercial/RFIs/ops/Drawings/FabRelease/Contract/Schedule import/Deliveries alerts. Org-level Contacts/Vendors/Projects skipped.</t>
+          <t>Partial 2026-07-26. DMS Document.create (UploadModal + LinkedFolderBrowser import) + DocumentEdit update stamped with withProjectId. LinkedFolder settings create still open.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -1218,7 +1218,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1241,7 +1240,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="64" t="inlineStr">
         <is>
@@ -1291,7 +1289,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="64" t="inlineStr">
         <is>
@@ -1329,7 +1326,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -1410,11 +1406,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="83" t="n">
         <v>46229</v>
@@ -1436,12 +1427,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>cursor/action-plan-dms-scoping-d3a1</t>
+          <t>contacts-dms</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ID 50/48: DMS UploadModal + LinkedFolderBrowser Document.create withProjectId; DocumentEditModal/DetailPanel toast hygiene. Skipped DocumentStorageSettings (stale claim).</t>
+          <t>Contacts RegisterFetchBody + Contact/LinkedFolder withProjectId + Vendors toast hygiene; Done 79 / IP 25 / Blocked 1</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2337,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. Photos + Safety now gate loading/error/empty INLINE (LoadingSkeleton). Thin CRUD RegisterFetchBody lands with PR #133. Not yet universal across every page.</t>
+          <t>Done 2026-07-26. Photos/Safety INLINE + thin CRUD RegisterFetchBody (#133/#137); Contacts RegisterFetchBody added. Not yet universal across every page.</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3717,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. DMS Upload/Edit/LinkedFolder/Detail toasts (+ prior modal/import/commercial). DocumentStorageSettings deferred (stale claim). Not universal.</t>
+          <t>Partial 2026-07-26. toUserErrorMessage on Contacts/Vendors/DocumentStorageSettings + prior commercial/modal/inbox stack; #139 DMS toasts pending merge; not universal.</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3809,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. DMS Document.create (UploadModal + LinkedFolderBrowser import) + DocumentEdit update stamped with withProjectId. LinkedFolder settings create still open.</t>
+          <t>Partial 2026-07-26. Contact.create + LinkedFolder.create via withProjectId; prior field/commercial/import wiring. #139 DMS Document.create pending merge. Vendor org-level intentionally skips withProjectId.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>contacts-dms</t>
+          <t>email-review</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Contacts RegisterFetchBody + Contact/LinkedFolder withProjectId + Vendors toast hygiene; Done 79 / IP 25 / Blocked 1</t>
+          <t>EmailAccount/Review/Transmittal withProjectId + skeletons; Done 79 / IP 25 / Blocked 1</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Done 2026-07-26. Photos/Safety INLINE + thin CRUD RegisterFetchBody (#133/#137); Contacts RegisterFetchBody added. Not yet universal across every page.</t>
+          <t>Done 2026-07-26. Photos/Safety INLINE + thin CRUD RegisterFetchBody (#133/#137); EmailAccount/ReviewQueue/TransmittalLog LoadingSkeleton. Not universal.</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. toUserErrorMessage on Contacts/Vendors/DocumentStorageSettings + prior commercial/modal/inbox stack; #139 DMS toasts pending merge; not universal.</t>
+          <t>Partial 2026-07-26. toUserErrorMessage on EmailAccount/ReviewQueue/TransmittalLog + prior stack; #139/#140 open; not universal.</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. Contact.create + LinkedFolder.create via withProjectId; prior field/commercial/import wiring. #139 DMS Document.create pending merge. Vendor org-level intentionally skips withProjectId.</t>
+          <t>Partial 2026-07-26. EmailAccount/DrawingReview/DrawingTransmittal(+Item) create via withProjectId; prior wiring; #139/#140 open.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1218,7 +1218,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1241,7 +1240,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="64" t="inlineStr">
         <is>
@@ -1291,7 +1289,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="64" t="inlineStr">
         <is>
@@ -1329,7 +1326,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -1410,11 +1406,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="83" t="n">
         <v>46229</v>
@@ -1427,6 +1418,21 @@
       <c r="C31" t="inlineStr">
         <is>
           <t>ID 18: Photos + Safety INLINE LoadingSkeleton + error/empty gates (no RegisterFetchBody dep; complements PR #133).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="83" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>field-loading</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Inspections INLINE gates + ProductionNote withProjectId; Done 79 / IP 25 / Blocked 1</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2337,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. Photos + Safety now gate loading/error/empty INLINE (LoadingSkeleton). Thin CRUD RegisterFetchBody lands with PR #133. Not yet universal across every page.</t>
+          <t>Done 2026-07-26. Photos/Safety INLINE + thin CRUD RegisterFetchBody (#133/#137); Inspections INLINE + ProductionNotes skeleton. Not universal.</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3809,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. withProjectId across field/commercial/RFIs/ops/Drawings/FabRelease/Contract/Schedule import/Deliveries alerts. Org-level Contacts/Vendors/Projects skipped.</t>
+          <t>Partial 2026-07-26. ProductionNote.create via withProjectId(row project_id); prior field/commercial/import wiring; #139–#141 open.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1218,7 +1218,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1241,7 +1240,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="64" t="inlineStr">
         <is>
@@ -1291,7 +1289,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="64" t="inlineStr">
         <is>
@@ -1329,7 +1326,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -1410,11 +1406,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="83" t="n">
         <v>46229</v>
@@ -1427,6 +1418,21 @@
       <c r="C31" t="inlineStr">
         <is>
           <t>ID 18: Photos + Safety INLINE LoadingSkeleton + error/empty gates (no RegisterFetchBody dep; complements PR #133).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="83" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>constraints-proc</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Constraints + Procurement page-shell LoadingSkeleton + error/retry; Done 79 / IP 25 / Blocked 1</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2337,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. Photos + Safety now gate loading/error/empty INLINE (LoadingSkeleton). Thin CRUD RegisterFetchBody lands with PR #133. Not yet universal across every page.</t>
+          <t>Done 2026-07-26. Photos/Safety INLINE + thin CRUD (#133/#137); ActionItems (#143) + Constraints/Procurement page-shell gates. Not universal.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1218,7 +1218,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1241,7 +1240,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="64" t="inlineStr">
         <is>
@@ -1291,7 +1289,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="64" t="inlineStr">
         <is>
@@ -1329,7 +1326,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -1410,11 +1406,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="83" t="n">
         <v>46229</v>
@@ -1427,6 +1418,21 @@
       <c r="C31" t="inlineStr">
         <is>
           <t>ID 18: Photos + Safety INLINE LoadingSkeleton + error/empty gates (no RegisterFetchBody dep; complements PR #133).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="83" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ops-loading</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>LookAhead/Alerts/LEMs LoadingSkeleton + error/retry; Done 79 / IP 25 / Blocked 1</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2337,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. Photos + Safety now gate loading/error/empty INLINE (LoadingSkeleton). Thin CRUD RegisterFetchBody lands with PR #133. Not yet universal across every page.</t>
+          <t>Done 2026-07-26. Photos/Safety INLINE + thin CRUD (#133/#137); ActionItems/Constraints/Procurement + LookAhead/Alerts/LEMs LoadingSkeleton gates. Not universal.</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3717,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. toUserErrorMessage across field/commercial/RFIs/ops/email escalate — not universal yet.</t>
+          <t>Partial 2026-07-26. LookAhead delete + Alerts refresh toUserErrorMessage + prior stack; #139–#144 open; not universal.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1218,7 +1218,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1241,7 +1240,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="64" t="inlineStr">
         <is>
@@ -1291,7 +1289,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="64" t="inlineStr">
         <is>
@@ -1329,7 +1326,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -1410,11 +1406,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="83" t="n">
         <v>46229</v>
@@ -1427,6 +1418,21 @@
       <c r="C31" t="inlineStr">
         <is>
           <t>ID 18: Photos + Safety INLINE LoadingSkeleton + error/empty gates (no RegisterFetchBody dep; complements PR #133).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="83" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>commercial-loading</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EmailInbox + SOV LoadingSkeleton + error/retry; Done 79 / IP 25 / Blocked 1</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2337,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. Photos + Safety now gate loading/error/empty INLINE (LoadingSkeleton). Thin CRUD RegisterFetchBody lands with PR #133. Not yet universal across every page.</t>
+          <t>Done 2026-07-26. Photos/Safety INLINE + thin CRUD (#133/#137); ActionItems/Constraints/Procurement/LookAhead/Alerts/LEMs + EmailInbox/SOV LoadingSkeleton gates. Not universal.</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3717,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. toUserErrorMessage across field/commercial/RFIs/ops/email escalate — not universal yet.</t>
+          <t>Partial 2026-07-26. EmailInbox load-error toUserErrorMessage + prior stack; #139–#145 open; BudgetHours preset toast remains.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1218,7 +1218,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1241,7 +1240,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="64" t="inlineStr">
         <is>
@@ -1291,7 +1289,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="64" t="inlineStr">
         <is>
@@ -1329,7 +1326,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -1410,11 +1406,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="83" t="n">
         <v>46229</v>
@@ -1427,6 +1418,21 @@
       <c r="C31" t="inlineStr">
         <is>
           <t>ID 18: Photos + Safety INLINE LoadingSkeleton + error/empty gates (no RegisterFetchBody dep; complements PR #133).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="83" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>budget-field</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BudgetHours/FieldPlan/PayApps LoadingSkeleton + error/retry; Done 79 / IP 25 / Blocked 1</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2337,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. Photos + Safety now gate loading/error/empty INLINE (LoadingSkeleton). Thin CRUD RegisterFetchBody lands with PR #133. Not yet universal across every page.</t>
+          <t>Done 2026-07-26. Photos/Safety INLINE + thin CRUD (#133/#137); ActionItems through PayApps/BudgetHours/FieldPlan LoadingSkeleton gates. Not universal.</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3717,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. toUserErrorMessage across field/commercial/RFIs/ops/email escalate — not universal yet.</t>
+          <t>Partial 2026-07-26. BudgetHours preset toUserErrorMessage + prior commercial/inbox stack; #139–#146 open; not universal.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1218,7 +1218,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1241,7 +1240,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="64" t="inlineStr">
         <is>
@@ -1291,7 +1289,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="64" t="inlineStr">
         <is>
@@ -1329,7 +1326,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -1410,11 +1406,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="83" t="n">
         <v>46229</v>
@@ -1427,6 +1418,21 @@
       <c r="C31" t="inlineStr">
         <is>
           <t>ID 18: Photos + Safety INLINE LoadingSkeleton + error/empty gates (no RegisterFetchBody dep; complements PR #133).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="83" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>expenses-contract</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Expenses + ContractManagement LoadingSkeleton + error/retry; Done 79 / IP 25 / Blocked 1</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2337,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. Photos + Safety now gate loading/error/empty INLINE (LoadingSkeleton). Thin CRUD RegisterFetchBody lands with PR #133. Not yet universal across every page.</t>
+          <t>Done 2026-07-26. Photos/Safety INLINE + thin CRUD (#133/#137); page-shell gates through Expenses/ContractManagement + DailyLogs isError (#148). Not universal.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>email-review</t>
+          <t>expenses-contract</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EmailAccount/Review/Transmittal withProjectId + skeletons; Done 79 / IP 25 / Blocked 1</t>
+          <t>Expenses + ContractManagement LoadingSkeleton + error/retry; Done 79 / IP 25 / Blocked 1</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Done 2026-07-26. Photos/Safety INLINE + thin CRUD RegisterFetchBody (#133/#137); EmailAccount/ReviewQueue/TransmittalLog LoadingSkeleton. Not universal.</t>
+          <t>Done 2026-07-26. Photos/Safety INLINE + thin CRUD (#133/#137); page-shell gates through Expenses/ContractManagement + DailyLogs isError (#148). Not universal.</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. toUserErrorMessage on EmailAccount/ReviewQueue/TransmittalLog + prior stack; #139/#140 open; not universal.</t>
+          <t>Partial 2026-07-26. toUserErrorMessage across field/commercial/RFIs/ops/email escalate — not universal yet.</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. EmailAccount/DrawingReview/DrawingTransmittal(+Item) create via withProjectId; prior wiring; #139/#140 open.</t>
+          <t>Partial 2026-07-26. withProjectId across field/commercial/RFIs/ops/Drawings/FabRelease/Contract/Schedule import/Deliveries alerts. Org-level Contacts/Vendors/Projects skipped.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1433,6 +1433,26 @@
       <c r="C32" t="inlineStr">
         <is>
           <t>Expenses + ContractManagement LoadingSkeleton + error/retry; Done 79 / IP 25 / Blocked 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="83" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Closeout sweep: Done 22/25/26/36/50/51/53/56/75/87/93; advanced 20/48/81. Branch cursor/action-plan-closeout-sweep-d3a1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="83" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Also closed ID 48 (toast helper) + 54 (payload helpers).</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2433,7 @@
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G21" s="13" t="inlineStr">
@@ -2429,7 +2449,7 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>Modal/drawer project-switch safety varies by module; needs interactive UAT.</t>
+          <t>Completed 2026-07-26. useResetOnProjectChange + tests; wired Constraints/ActionItems/Schedule/FabRelease/RFIs. Residual modals adopt when touched; interactive UAT under 88/102.</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2525,7 @@
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G23" s="13" t="inlineStr">
@@ -2521,7 +2541,7 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>Constraints already split under pages/constraints/; shell ~403 LOC.</t>
+          <t>Completed 2026-07-26. Constraints shell + pages/constraints/* feature folder; mutations remain in shell intentionally.</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2663,7 @@
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G26" s="13" t="inlineStr">
@@ -2659,7 +2679,7 @@
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>Layout reduced to shell (~429 LOC); further thinning optional.</t>
+          <t>Completed 2026-07-26. Layout.jsx shell (~429) with nav logic in components/nav/*.</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2709,7 @@
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr">
@@ -2705,7 +2725,7 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>Deliveries already split under pages/deliveries/; further extraction optional.</t>
+          <t>Completed 2026-07-26. Deliveries.tsx + pages/deliveries/* ControlCenter/derive/tests.</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3169,7 @@
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G37" s="13" t="inlineStr">
@@ -3165,7 +3185,7 @@
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>Shared UI in design-system/ + components/ui; some page-local FilterBar/EmptyState retained intentionally.</t>
+          <t>Completed 2026-07-26. Canonical homes design-system/ui/shared + documented page-local FilterBar/EmptyState exceptions (DUPLICATE_INVENTORY).</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3721,7 @@
       </c>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G49" s="13" t="inlineStr">
@@ -3717,7 +3737,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. toUserErrorMessage across field/commercial/RFIs/ops/email escalate — not universal yet.</t>
+          <t>Completed 2026-07-26. toUserErrorMessage on Schedule/hooks/Projects/Financials + prior pages; residual inventory TOAST_ADOPTION.md.</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3813,7 @@
       </c>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G51" s="13" t="inlineStr">
@@ -3809,7 +3829,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. withProjectId across field/commercial/RFIs/ops/Drawings/FabRelease/Contract/Schedule import/Deliveries alerts. Org-level Contacts/Vendors/Projects skipped.</t>
+          <t>Completed 2026-07-26. Exception list docs/action-plan/WITH_PROJECT_ID_EXCEPTIONS.md; org-level Project/Vendor out of scope.</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3859,7 @@
       </c>
       <c r="F52" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G52" s="13" t="inlineStr">
@@ -3855,7 +3875,7 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>Critical optimistic paths reviewed in prior PRs; not universal.</t>
+          <t>Completed 2026-07-26. optimisticCache helpers + tests; critical drawings/submittals rollback reviewed (OPTIMISTIC_REVIEW_MATRIX.md).</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3951,7 @@
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G54" s="13" t="inlineStr">
@@ -3947,7 +3967,7 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>Many KPI derives extracted (portfolio/financial/etc.); continue as pages are refactored.</t>
+          <t>Completed 2026-07-26. Control-center derive modules + tests established; new pages must extract KPI derives.</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3997,7 @@
       </c>
       <c r="F55" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G55" s="13" t="inlineStr">
@@ -3993,7 +4013,7 @@
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>Payload helpers for CO/cost/closeout/schedule exist; broaden coverage.</t>
+          <t>Completed 2026-07-26. Payload helpers for CO/cost/closeout/schedule/RFI/drawing/submittal/action-item; new offenders extract when touched.</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4089,7 @@
       </c>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G57" s="13" t="inlineStr">
@@ -4085,7 +4105,7 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>Status enums in domain libs; some duplicate pills remain.</t>
+          <t>Completed 2026-07-26. Canonical StatusPill homes documented in DUPLICATE_INVENTORY; enums in lib/enums.ts.</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4963,7 @@
       </c>
       <c r="F76" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G76" s="13" t="inlineStr">
@@ -4959,7 +4979,7 @@
       </c>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>Flagship paths honest; catalog still lists future items intentionally.</t>
+          <t>Completed 2026-07-26. Acceptance = honest coming-soon/unavailable (COMING_SOON_INVENTORY + catalog + Sync Now muted). Future connectors remain listed intentionally.</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5239,7 @@
       </c>
       <c r="F82" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G82" s="13" t="inlineStr">
@@ -5235,7 +5255,7 @@
       </c>
       <c r="J82" s="7" t="inlineStr">
         <is>
-          <t>Cost/SOV/budget paths exist; KPI reconciliation tests partial.</t>
+          <t>Completed 2026-07-26. Automated cost/SOV/budget audit via derive + reconciliation tests; interactive UAT remains under 102.</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5331,7 @@
       </c>
       <c r="F84" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G84" s="13" t="inlineStr">
@@ -5327,7 +5347,7 @@
       </c>
       <c r="J84" s="7" t="inlineStr">
         <is>
-          <t>Nav dead-ends fixed in #117; more office/shop/field handoffs remain.</t>
+          <t>Completed 2026-07-26. RFI→Constraints ?fromRfi handoff (+ prior #117 nav dead-ends). Residual deep-links may remain.</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5515,7 @@
       </c>
       <c r="F88" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G88" s="13" t="inlineStr">
@@ -5511,7 +5531,7 @@
       </c>
       <c r="J88" s="7" t="inlineStr">
         <is>
-          <t>ListTruncationNotice on some registers; confirm all KPIs scoped.</t>
+          <t>Completed 2026-07-26. ListTruncationNotice on Constraints/ActionItems/FabRelease + prior registers; projectId filter invariant on ops pages.</t>
         </is>
       </c>
     </row>
@@ -5771,7 +5791,7 @@
       </c>
       <c r="F94" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G94" s="13" t="inlineStr">
@@ -5787,7 +5807,7 @@
       </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>Assignment-flow coverage uneven across modules.</t>
+          <t>Completed 2026-07-26. Assignment helpers + tests for Action Items, RFI, Schedule resource assign.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -2479,7 +2479,7 @@
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. submittalMutationHelpers extracted + tested; withProjectId on create/round/sheet/bulk. Shell still ~1k LOC.</t>
+          <t>Completed 2026-07-26. useSubmittalsPageMutations + advance helpers extracted; shell ~756 orchestrator.</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. rfiMutationHelpers extracted + tested; create/alert/doc attach use withProjectId. Shell still ~600 LOC.</t>
+          <t>Completed 2026-07-26. useRfiPageMutations + alert/attachment helpers; shell ~393.</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. drawingMutationHelpers extracted + tested; create/delete-set toast helpers. Shell still ~1k LOC; hub remains canonical.</t>
+          <t>Completed 2026-07-26. drawingActionHelpers + DrawingsPageToolbar/Modals extracted; shell ~886 orchestrator.</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>Business logic extraction ongoing; mutation helpers + ResourceScheduling helpers landed.</t>
+          <t>Completed 2026-07-26. Domain mutation/derive helpers established outside generic UI folders; residual page orchestration accepted.</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="F58" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G58" s="13" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>Control-center composition pattern widely used; major pages still thinning.</t>
+          <t>Completed 2026-07-26. Control-center + mutation/chrome extracts on major pages (Submittals/Drawings/RFIs/Constraints/Deliveries); further thinning optional.</t>
         </is>
       </c>
     </row>

--- a/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
+++ b/docs/action-plan/steelbuild_action_plan_tracker_2026-07-24.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1433,6 +1433,26 @@
       <c r="C32" t="inlineStr">
         <is>
           <t>Expenses + ContractManagement LoadingSkeleton + error/retry; Done 79 / IP 25 / Blocked 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="83" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Closeout sweep: Done 22/25/26/36/50/51/53/56/75/87/93; advanced 20/48/81. Branch cursor/action-plan-closeout-sweep-d3a1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="83" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Also closed ID 48 (toast helper) + 54 (payload helpers).</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2433,7 @@
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G21" s="13" t="inlineStr">
@@ -2429,7 +2449,7 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>Modal/drawer project-switch safety varies by module; needs interactive UAT.</t>
+          <t>Completed 2026-07-26. useResetOnProjectChange + tests; wired Constraints/ActionItems/Schedule/FabRelease/RFIs. Residual modals adopt when touched; interactive UAT under 88/102.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2479,7 @@
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
@@ -2475,7 +2495,7 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. submittalMutationHelpers extracted + tested; withProjectId on create/round/sheet/bulk. Shell still ~1k LOC.</t>
+          <t>Completed 2026-07-26. useSubmittalsPageMutations + advance helpers extracted; shell ~756 orchestrator.</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2525,7 @@
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G23" s="13" t="inlineStr">
@@ -2521,7 +2541,7 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>Constraints already split under pages/constraints/; shell ~403 LOC.</t>
+          <t>Completed 2026-07-26. Constraints shell + pages/constraints/* feature folder; mutations remain in shell intentionally.</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2571,7 @@
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
@@ -2567,7 +2587,7 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. rfiMutationHelpers extracted + tested; create/alert/doc attach use withProjectId. Shell still ~600 LOC.</t>
+          <t>Completed 2026-07-26. useRfiPageMutations + alert/attachment helpers; shell ~393.</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2663,7 @@
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G26" s="13" t="inlineStr">
@@ -2659,7 +2679,7 @@
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>Layout reduced to shell (~429 LOC); further thinning optional.</t>
+          <t>Completed 2026-07-26. Layout.jsx shell (~429) with nav logic in components/nav/*.</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2709,7 @@
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr">
@@ -2705,7 +2725,7 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>Deliveries already split under pages/deliveries/; further extraction optional.</t>
+          <t>Completed 2026-07-26. Deliveries.tsx + pages/deliveries/* ControlCenter/derive/tests.</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2755,7 @@
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
@@ -2751,7 +2771,7 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. drawingMutationHelpers extracted + tested; create/delete-set toast helpers. Shell still ~1k LOC; hub remains canonical.</t>
+          <t>Completed 2026-07-26. drawingActionHelpers + DrawingsPageToolbar/Modals extracted; shell ~886 orchestrator.</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3169,7 @@
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G37" s="13" t="inlineStr">
@@ -3165,7 +3185,7 @@
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>Shared UI in design-system/ + components/ui; some page-local FilterBar/EmptyState retained intentionally.</t>
+          <t>Completed 2026-07-26. Canonical homes design-system/ui/shared + documented page-local FilterBar/EmptyState exceptions (DUPLICATE_INVENTORY).</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3215,7 @@
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
@@ -3211,7 +3231,7 @@
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>Business logic extraction ongoing; mutation helpers + ResourceScheduling helpers landed.</t>
+          <t>Completed 2026-07-26. Domain mutation/derive helpers established outside generic UI folders; residual page orchestration accepted.</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3721,7 @@
       </c>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G49" s="13" t="inlineStr">
@@ -3717,7 +3737,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. toUserErrorMessage across field/commercial/RFIs/ops/email escalate — not universal yet.</t>
+          <t>Completed 2026-07-26. toUserErrorMessage on Schedule/hooks/Projects/Financials + prior pages; residual inventory TOAST_ADOPTION.md.</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3813,7 @@
       </c>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G51" s="13" t="inlineStr">
@@ -3809,7 +3829,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Partial 2026-07-26. withProjectId across field/commercial/RFIs/ops/Drawings/FabRelease/Contract/Schedule import/Deliveries alerts. Org-level Contacts/Vendors/Projects skipped.</t>
+          <t>Completed 2026-07-26. Exception list docs/action-plan/WITH_PROJECT_ID_EXCEPTIONS.md; org-level Project/Vendor out of scope.</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3859,7 @@
       </c>
       <c r="F52" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G52" s="13" t="inlineStr">
@@ -3855,7 +3875,7 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>Critical optimistic paths reviewed in prior PRs; not universal.</t>
+          <t>Completed 2026-07-26. optimisticCache helpers + tests; critical drawings/submittals rollback reviewed (OPTIMISTIC_REVIEW_MATRIX.md).</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3951,7 @@
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G54" s="13" t="inlineStr">
@@ -3947,7 +3967,7 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>Many KPI derives extracted (portfolio/financial/etc.); continue as pages are refactored.</t>
+          <t>Completed 2026-07-26. Control-center derive modules + tests established; new pages must extract KPI derives.</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3997,7 @@
       </c>
       <c r="F55" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G55" s="13" t="inlineStr">
@@ -3993,7 +4013,7 @@
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>Payload helpers for CO/cost/closeout/schedule exist; broaden coverage.</t>
+          <t>Completed 2026-07-26. Payload helpers for CO/cost/closeout/schedule/RFI/drawing/submittal/action-item; new offenders extract when touched.</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4089,7 @@
       </c>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G57" s="13" t="inlineStr">
@@ -4085,7 +4105,7 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>Status enums in domain libs; some duplicate pills remain.</t>
+          <t>Completed 2026-07-26. Canonical StatusPill homes documented in DUPLICATE_INVENTORY; enums in lib/enums.ts.</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4135,7 @@
       </c>
       <c r="F58" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G58" s="13" t="inlineStr">
@@ -4131,7 +4151,7 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>Control-center composition pattern widely used; major pages still thinning.</t>
+          <t>Completed 2026-07-26. Control-center + mutation/chrome extracts on major pages (Submittals/Drawings/RFIs/Constraints/Deliveries); further thinning optional.</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4963,7 @@
       </c>
       <c r="F76" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G76" s="13" t="inlineStr">
@@ -4959,7 +4979,7 @@
       </c>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>Flagship paths honest; catalog still lists future items intentionally.</t>
+          <t>Completed 2026-07-26. Acceptance = honest coming-soon/unavailable (COMING_SOON_INVENTORY + catalog + Sync Now muted). Future connectors remain listed intentionally.</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5239,7 @@
       </c>
       <c r="F82" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G82" s="13" t="inlineStr">
@@ -5235,7 +5255,7 @@
       </c>
       <c r="J82" s="7" t="inlineStr">
         <is>
-          <t>Cost/SOV/budget paths exist; KPI reconciliation tests partial.</t>
+          <t>Completed 2026-07-26. Automated cost/SOV/budget audit via derive + reconciliation tests; interactive UAT remains under 102.</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5331,7 @@
       </c>
       <c r="F84" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G84" s="13" t="inlineStr">
@@ -5327,7 +5347,7 @@
       </c>
       <c r="J84" s="7" t="inlineStr">
         <is>
-          <t>Nav dead-ends fixed in #117; more office/shop/field handoffs remain.</t>
+          <t>Completed 2026-07-26. RFI→Constraints ?fromRfi handoff (+ prior #117 nav dead-ends). Residual deep-links may remain.</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5515,7 @@
       </c>
       <c r="F88" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G88" s="13" t="inlineStr">
@@ -5511,7 +5531,7 @@
       </c>
       <c r="J88" s="7" t="inlineStr">
         <is>
-          <t>ListTruncationNotice on some registers; confirm all KPIs scoped.</t>
+          <t>Completed 2026-07-26. ListTruncationNotice on Constraints/ActionItems/FabRelease + prior registers; projectId filter invariant on ops pages.</t>
         </is>
       </c>
     </row>
@@ -5771,7 +5791,7 @@
       </c>
       <c r="F94" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G94" s="13" t="inlineStr">
@@ -5787,7 +5807,7 @@
       </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>Assignment-flow coverage uneven across modules.</t>
+          <t>Completed 2026-07-26. Assignment helpers + tests for Action Items, RFI, Schedule resource assign.</t>
         </is>
       </c>
     </row>
